--- a/jogos_2024-11-12.xlsx
+++ b/jogos_2024-11-12.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Uruguay Primera División</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>3.15</v>
       </c>
       <c r="M3" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>3.95</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>2.89</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2.51</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.1</v>
+        <v>4.47</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['41', '61', '88']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['15', '65']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>3.6</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45608.79166666666</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uruguay Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.15</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.95</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.89</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.51</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.47</v>
+        <v>3.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '61', '88']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['15', '65']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.59</v>
+        <v>1.06</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>2.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.29</v>
+        <v>1.33</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.83</v>
+        <v>3.6</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45608.79166666666</v>
